--- a/docs/副本广告数据昆明.xlsx
+++ b/docs/副本广告数据昆明.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\orderDevelop\my-vue\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C878DA7-1CA6-479A-82D3-DDF24E1B33A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6344FC47-CCDB-4E2D-A8BC-A131D48B5794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11952" yWindow="420" windowWidth="21600" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="660" yWindow="384" windowWidth="15336" windowHeight="10776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -734,17 +734,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J318"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.875" customWidth="1"/>
-    <col min="2" max="3" width="18.75" customWidth="1"/>
-    <col min="4" max="4" width="18.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="2" max="3" width="18.77734375" customWidth="1"/>
+    <col min="4" max="4" width="18.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -767,7 +767,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>45778</v>
       </c>
@@ -782,7 +782,7 @@
       <c r="F2" s="12"/>
       <c r="G2" s="13"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>45779</v>
       </c>
@@ -797,7 +797,7 @@
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>45780</v>
       </c>
@@ -812,7 +812,7 @@
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>45781</v>
       </c>
@@ -827,7 +827,7 @@
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>45782</v>
       </c>
@@ -844,7 +844,7 @@
       </c>
       <c r="G6" s="13"/>
     </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>45783</v>
       </c>
@@ -865,7 +865,7 @@
       </c>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>45784</v>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="G8" s="13"/>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>45785</v>
       </c>
@@ -907,7 +907,7 @@
       </c>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>45786</v>
       </c>
@@ -928,7 +928,7 @@
       </c>
       <c r="G10" s="13"/>
     </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>45787</v>
       </c>
@@ -949,7 +949,7 @@
       </c>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>45788</v>
       </c>
@@ -970,7 +970,7 @@
       </c>
       <c r="G12" s="13"/>
     </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>45789</v>
       </c>
@@ -989,7 +989,7 @@
       </c>
       <c r="G13" s="13"/>
     </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>45790</v>
       </c>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G14" s="13"/>
     </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>45791</v>
       </c>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G15" s="13"/>
     </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>45792</v>
       </c>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="G16" s="13"/>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>45793</v>
       </c>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>45794</v>
       </c>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="G18" s="13"/>
     </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>45795</v>
       </c>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>45796</v>
       </c>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="G20" s="13"/>
     </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>45797</v>
       </c>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>45798</v>
       </c>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="G22" s="13"/>
     </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>45799</v>
       </c>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="G23" s="13"/>
     </row>
-    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>45800</v>
       </c>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G24" s="13"/>
     </row>
-    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>45801</v>
       </c>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>45802</v>
       </c>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G26" s="13"/>
     </row>
-    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>45803</v>
       </c>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>45804</v>
       </c>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G28" s="13"/>
     </row>
-    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>45805</v>
       </c>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>45806</v>
       </c>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G30" s="13"/>
     </row>
-    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>45807</v>
       </c>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>45808</v>
       </c>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="G32" s="13"/>
     </row>
-    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>45809</v>
       </c>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>45810</v>
       </c>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G34" s="13"/>
     </row>
-    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>45811</v>
       </c>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>45812</v>
       </c>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G36" s="13"/>
     </row>
-    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>45813</v>
       </c>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>45814</v>
       </c>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="G38" s="13"/>
     </row>
-    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>45815</v>
       </c>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>45816</v>
       </c>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G40" s="13"/>
     </row>
-    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>45817</v>
       </c>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="G41" s="13"/>
     </row>
-    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>45818</v>
       </c>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G42" s="13"/>
     </row>
-    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>45819</v>
       </c>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G43" s="13"/>
     </row>
-    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>45820</v>
       </c>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="G44" s="13"/>
     </row>
-    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>45821</v>
       </c>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>45822</v>
       </c>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G46" s="13"/>
     </row>
-    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>45823</v>
       </c>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>45824</v>
       </c>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G48" s="13"/>
     </row>
-    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>45825</v>
       </c>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>45826</v>
       </c>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G50" s="13"/>
     </row>
-    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>45827</v>
       </c>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>45828</v>
       </c>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G52" s="13"/>
     </row>
-    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>45829</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G53" s="13"/>
     </row>
-    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>45830</v>
       </c>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G54" s="13"/>
     </row>
-    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>45831</v>
       </c>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G55" s="13"/>
     </row>
-    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>45832</v>
       </c>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="G56" s="13"/>
     </row>
-    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>45833</v>
       </c>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G57" s="13"/>
     </row>
-    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>45834</v>
       </c>
@@ -1871,7 +1871,9 @@
       <c r="C58" s="10">
         <v>4762</v>
       </c>
-      <c r="D58" s="6"/>
+      <c r="D58" s="6">
+        <v>43</v>
+      </c>
       <c r="E58" s="7">
         <v>286.31</v>
       </c>
@@ -1880,7 +1882,7 @@
       </c>
       <c r="G58" s="13"/>
     </row>
-    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>45835</v>
       </c>
@@ -1890,7 +1892,9 @@
       <c r="C59" s="10">
         <v>6904</v>
       </c>
-      <c r="D59" s="6"/>
+      <c r="D59" s="6">
+        <v>62</v>
+      </c>
       <c r="E59" s="7">
         <v>405.23</v>
       </c>
@@ -1899,7 +1903,7 @@
       </c>
       <c r="G59" s="13"/>
     </row>
-    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>45836</v>
       </c>
@@ -1909,7 +1913,9 @@
       <c r="C60" s="10">
         <v>3174</v>
       </c>
-      <c r="D60" s="6"/>
+      <c r="D60" s="6">
+        <v>25</v>
+      </c>
       <c r="E60" s="7">
         <v>178.55</v>
       </c>
@@ -1918,7 +1924,7 @@
       </c>
       <c r="G60" s="13"/>
     </row>
-    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>45837</v>
       </c>
@@ -1935,7 +1941,7 @@
       </c>
       <c r="G61" s="13"/>
     </row>
-    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>45838</v>
       </c>
@@ -1952,7 +1958,7 @@
       </c>
       <c r="G62" s="13"/>
     </row>
-    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>45839</v>
       </c>
@@ -1969,7 +1975,7 @@
       </c>
       <c r="G63" s="13"/>
     </row>
-    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>45840</v>
       </c>
@@ -1986,7 +1992,7 @@
       </c>
       <c r="G64" s="13"/>
     </row>
-    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>45841</v>
       </c>
@@ -2007,7 +2013,7 @@
       </c>
       <c r="G65" s="13"/>
     </row>
-    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>45842</v>
       </c>
@@ -2028,7 +2034,7 @@
       </c>
       <c r="G66" s="13"/>
     </row>
-    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>45843</v>
       </c>
@@ -2049,7 +2055,7 @@
       </c>
       <c r="G67" s="13"/>
     </row>
-    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>45844</v>
       </c>
@@ -2070,7 +2076,7 @@
       </c>
       <c r="G68" s="13"/>
     </row>
-    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A69" s="9">
         <v>45845</v>
       </c>
@@ -2091,7 +2097,7 @@
       </c>
       <c r="G69" s="13"/>
     </row>
-    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>45846</v>
       </c>
@@ -2112,7 +2118,7 @@
       </c>
       <c r="G70" s="13"/>
     </row>
-    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>45847</v>
       </c>
@@ -2133,7 +2139,7 @@
       </c>
       <c r="G71" s="13"/>
     </row>
-    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>45848</v>
       </c>
@@ -2154,7 +2160,7 @@
       </c>
       <c r="G72" s="13"/>
     </row>
-    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>45849</v>
       </c>
@@ -2175,7 +2181,7 @@
       </c>
       <c r="G73" s="13"/>
     </row>
-    <row r="74" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>45850</v>
       </c>
@@ -2196,7 +2202,7 @@
       </c>
       <c r="G74" s="13"/>
     </row>
-    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
         <v>45851</v>
       </c>
@@ -2217,7 +2223,7 @@
       </c>
       <c r="G75" s="13"/>
     </row>
-    <row r="76" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>45852</v>
       </c>
@@ -2238,7 +2244,7 @@
       </c>
       <c r="G76" s="13"/>
     </row>
-    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>45853</v>
       </c>
@@ -2259,7 +2265,7 @@
       </c>
       <c r="G77" s="13"/>
     </row>
-    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>45854</v>
       </c>
@@ -2280,7 +2286,7 @@
       </c>
       <c r="G78" s="13"/>
     </row>
-    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>45855</v>
       </c>
@@ -2301,7 +2307,7 @@
       </c>
       <c r="G79" s="13"/>
     </row>
-    <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>45856</v>
       </c>
@@ -2318,7 +2324,7 @@
       </c>
       <c r="G80" s="13"/>
     </row>
-    <row r="81" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A81" s="9">
         <v>45857</v>
       </c>
@@ -2339,7 +2345,7 @@
       </c>
       <c r="G81" s="13"/>
     </row>
-    <row r="82" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>45858</v>
       </c>
@@ -2360,7 +2366,7 @@
       </c>
       <c r="G82" s="13"/>
     </row>
-    <row r="83" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>45859</v>
       </c>
@@ -2381,7 +2387,7 @@
       </c>
       <c r="G83" s="13"/>
     </row>
-    <row r="84" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>45860</v>
       </c>
@@ -2402,7 +2408,7 @@
       </c>
       <c r="G84" s="13"/>
     </row>
-    <row r="85" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>45861</v>
       </c>
@@ -2423,7 +2429,7 @@
       </c>
       <c r="G85" s="13"/>
     </row>
-    <row r="86" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>45862</v>
       </c>
@@ -2444,7 +2450,7 @@
       </c>
       <c r="G86" s="13"/>
     </row>
-    <row r="87" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>45863</v>
       </c>
@@ -2465,7 +2471,7 @@
       </c>
       <c r="G87" s="13"/>
     </row>
-    <row r="88" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>45864</v>
       </c>
@@ -2486,7 +2492,7 @@
       </c>
       <c r="G88" s="13"/>
     </row>
-    <row r="89" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A89" s="9">
         <v>45865</v>
       </c>
@@ -2507,7 +2513,7 @@
       </c>
       <c r="G89" s="13"/>
     </row>
-    <row r="90" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>45866</v>
       </c>
@@ -2528,7 +2534,7 @@
       </c>
       <c r="G90" s="13"/>
     </row>
-    <row r="91" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>45867</v>
       </c>
@@ -2549,7 +2555,7 @@
       </c>
       <c r="G91" s="13"/>
     </row>
-    <row r="92" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>45868</v>
       </c>
@@ -2570,7 +2576,7 @@
       </c>
       <c r="G92" s="13"/>
     </row>
-    <row r="93" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>45869</v>
       </c>
@@ -2591,7 +2597,7 @@
       </c>
       <c r="G93" s="13"/>
     </row>
-    <row r="94" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>45870</v>
       </c>
@@ -2612,7 +2618,7 @@
       </c>
       <c r="G94" s="13"/>
     </row>
-    <row r="95" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>45871</v>
       </c>
@@ -2633,7 +2639,7 @@
       </c>
       <c r="G95" s="13"/>
     </row>
-    <row r="96" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>45872</v>
       </c>
@@ -2654,7 +2660,7 @@
       </c>
       <c r="G96" s="13"/>
     </row>
-    <row r="97" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>45873</v>
       </c>
@@ -2677,7 +2683,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
         <v>45874</v>
       </c>
@@ -2698,7 +2704,7 @@
       </c>
       <c r="G98" s="13"/>
     </row>
-    <row r="99" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>45875</v>
       </c>
@@ -2719,7 +2725,7 @@
       </c>
       <c r="G99" s="13"/>
     </row>
-    <row r="100" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>45876</v>
       </c>
@@ -2740,7 +2746,7 @@
       </c>
       <c r="G100" s="13"/>
     </row>
-    <row r="101" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>45877</v>
       </c>
@@ -2761,7 +2767,7 @@
       </c>
       <c r="G101" s="13"/>
     </row>
-    <row r="102" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>45878</v>
       </c>
@@ -2782,7 +2788,7 @@
       </c>
       <c r="G102" s="13"/>
     </row>
-    <row r="103" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>45879</v>
       </c>
@@ -2803,7 +2809,7 @@
       </c>
       <c r="G103" s="13"/>
     </row>
-    <row r="104" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>45880</v>
       </c>
@@ -2824,7 +2830,7 @@
       </c>
       <c r="G104" s="13"/>
     </row>
-    <row r="105" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A105" s="9">
         <v>45881</v>
       </c>
@@ -2845,7 +2851,7 @@
       </c>
       <c r="G105" s="13"/>
     </row>
-    <row r="106" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
         <v>45882</v>
       </c>
@@ -2866,7 +2872,7 @@
       </c>
       <c r="G106" s="13"/>
     </row>
-    <row r="107" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>45883</v>
       </c>
@@ -2887,7 +2893,7 @@
       </c>
       <c r="G107" s="13"/>
     </row>
-    <row r="108" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>45884</v>
       </c>
@@ -2908,7 +2914,7 @@
       </c>
       <c r="G108" s="13"/>
     </row>
-    <row r="109" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>45885</v>
       </c>
@@ -2929,7 +2935,7 @@
       </c>
       <c r="G109" s="13"/>
     </row>
-    <row r="110" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>45886</v>
       </c>
@@ -2950,7 +2956,7 @@
       </c>
       <c r="G110" s="13"/>
     </row>
-    <row r="111" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A111" s="9">
         <v>45887</v>
       </c>
@@ -2971,7 +2977,7 @@
       </c>
       <c r="G111" s="13"/>
     </row>
-    <row r="112" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A112" s="9">
         <v>45888</v>
       </c>
@@ -2992,7 +2998,7 @@
       </c>
       <c r="G112" s="13"/>
     </row>
-    <row r="113" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A113" s="9">
         <v>45889</v>
       </c>
@@ -3013,7 +3019,7 @@
       </c>
       <c r="G113" s="13"/>
     </row>
-    <row r="114" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
         <v>45890</v>
       </c>
@@ -3034,7 +3040,7 @@
       </c>
       <c r="G114" s="13"/>
     </row>
-    <row r="115" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
         <v>45891</v>
       </c>
@@ -3055,7 +3061,7 @@
       </c>
       <c r="G115" s="13"/>
     </row>
-    <row r="116" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>45892</v>
       </c>
@@ -3076,7 +3082,7 @@
       </c>
       <c r="G116" s="13"/>
     </row>
-    <row r="117" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A117" s="9">
         <v>45893</v>
       </c>
@@ -3097,7 +3103,7 @@
       </c>
       <c r="G117" s="13"/>
     </row>
-    <row r="118" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>45894</v>
       </c>
@@ -3118,7 +3124,7 @@
       </c>
       <c r="G118" s="13"/>
     </row>
-    <row r="119" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A119" s="9">
         <v>45895</v>
       </c>
@@ -3139,7 +3145,7 @@
       </c>
       <c r="G119" s="13"/>
     </row>
-    <row r="120" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A120" s="9">
         <v>45896</v>
       </c>
@@ -3160,7 +3166,7 @@
       </c>
       <c r="G120" s="13"/>
     </row>
-    <row r="121" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A121" s="9">
         <v>45897</v>
       </c>
@@ -3181,7 +3187,7 @@
       </c>
       <c r="G121" s="13"/>
     </row>
-    <row r="122" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>45898</v>
       </c>
@@ -3202,7 +3208,7 @@
       </c>
       <c r="G122" s="13"/>
     </row>
-    <row r="123" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A123" s="9">
         <v>45899</v>
       </c>
@@ -3223,7 +3229,7 @@
       </c>
       <c r="G123" s="13"/>
     </row>
-    <row r="124" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>45900</v>
       </c>
@@ -3244,7 +3250,7 @@
       </c>
       <c r="G124" s="13"/>
     </row>
-    <row r="125" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A125" s="9">
         <v>45901</v>
       </c>
@@ -3265,7 +3271,7 @@
       </c>
       <c r="G125" s="13"/>
     </row>
-    <row r="126" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A126" s="9">
         <v>45902</v>
       </c>
@@ -3286,7 +3292,7 @@
       </c>
       <c r="G126" s="13"/>
     </row>
-    <row r="127" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A127" s="9">
         <v>45903</v>
       </c>
@@ -3307,7 +3313,7 @@
       </c>
       <c r="G127" s="13"/>
     </row>
-    <row r="128" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>45904</v>
       </c>
@@ -3328,7 +3334,7 @@
       </c>
       <c r="G128" s="13"/>
     </row>
-    <row r="129" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A129" s="9">
         <v>45905</v>
       </c>
@@ -3349,7 +3355,7 @@
       </c>
       <c r="G129" s="13"/>
     </row>
-    <row r="130" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A130" s="9">
         <v>45906</v>
       </c>
@@ -3370,7 +3376,7 @@
       </c>
       <c r="G130" s="13"/>
     </row>
-    <row r="131" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A131" s="9">
         <v>45907</v>
       </c>
@@ -3391,7 +3397,7 @@
       </c>
       <c r="G131" s="13"/>
     </row>
-    <row r="132" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>45908</v>
       </c>
@@ -3414,7 +3420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A133" s="9">
         <v>45909</v>
       </c>
@@ -3435,7 +3441,7 @@
       </c>
       <c r="G133" s="13"/>
     </row>
-    <row r="134" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A134" s="9">
         <v>45910</v>
       </c>
@@ -3456,7 +3462,7 @@
       </c>
       <c r="G134" s="13"/>
     </row>
-    <row r="135" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A135" s="9">
         <v>45911</v>
       </c>
@@ -3477,7 +3483,7 @@
       </c>
       <c r="G135" s="13"/>
     </row>
-    <row r="136" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>45912</v>
       </c>
@@ -3498,7 +3504,7 @@
       </c>
       <c r="G136" s="13"/>
     </row>
-    <row r="137" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>45913</v>
       </c>
@@ -3519,7 +3525,7 @@
       </c>
       <c r="G137" s="13"/>
     </row>
-    <row r="138" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>45914</v>
       </c>
@@ -3540,7 +3546,7 @@
       </c>
       <c r="G138" s="13"/>
     </row>
-    <row r="139" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A139" s="9">
         <v>45915</v>
       </c>
@@ -3561,7 +3567,7 @@
       </c>
       <c r="G139" s="13"/>
     </row>
-    <row r="140" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A140" s="9">
         <v>45916</v>
       </c>
@@ -3582,7 +3588,7 @@
       </c>
       <c r="G140" s="13"/>
     </row>
-    <row r="141" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A141" s="9">
         <v>45917</v>
       </c>
@@ -3603,7 +3609,7 @@
       </c>
       <c r="G141" s="13"/>
     </row>
-    <row r="142" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>45918</v>
       </c>
@@ -3614,7 +3620,7 @@
         <v>3406</v>
       </c>
       <c r="D142" s="13">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E142" s="7">
         <v>188.54</v>
@@ -3624,7 +3630,7 @@
       </c>
       <c r="G142" s="13"/>
     </row>
-    <row r="143" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A143" s="9">
         <v>45919</v>
       </c>
@@ -3635,7 +3641,7 @@
         <v>3792</v>
       </c>
       <c r="D143" s="13">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E143" s="7">
         <v>195.61</v>
@@ -3645,7 +3651,7 @@
       </c>
       <c r="G143" s="13"/>
     </row>
-    <row r="144" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A144" s="9">
         <v>45920</v>
       </c>
@@ -3656,7 +3662,7 @@
         <v>3786</v>
       </c>
       <c r="D144" s="13">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E144" s="7">
         <v>289.64</v>
@@ -3666,7 +3672,7 @@
       </c>
       <c r="G144" s="13"/>
     </row>
-    <row r="145" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A145" s="9">
         <v>45921</v>
       </c>
@@ -3677,7 +3683,7 @@
         <v>5112</v>
       </c>
       <c r="D145" s="13">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E145" s="7">
         <v>419.67</v>
@@ -3687,7 +3693,7 @@
       </c>
       <c r="G145" s="13"/>
     </row>
-    <row r="146" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A146" s="9">
         <v>45922</v>
       </c>
@@ -3698,7 +3704,7 @@
         <v>5956</v>
       </c>
       <c r="D146" s="13">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E146" s="7">
         <v>482.88</v>
@@ -3708,7 +3714,7 @@
       </c>
       <c r="G146" s="13"/>
     </row>
-    <row r="147" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A147" s="9">
         <v>45923</v>
       </c>
@@ -3719,7 +3725,7 @@
         <v>5411</v>
       </c>
       <c r="D147" s="13">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E147" s="7">
         <v>499.39</v>
@@ -3729,7 +3735,7 @@
       </c>
       <c r="G147" s="13"/>
     </row>
-    <row r="148" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A148" s="9">
         <v>45924</v>
       </c>
@@ -3740,7 +3746,7 @@
         <v>6112</v>
       </c>
       <c r="D148" s="13">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E148" s="7">
         <v>465.36</v>
@@ -3750,7 +3756,7 @@
       </c>
       <c r="G148" s="13"/>
     </row>
-    <row r="149" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A149" s="9">
         <v>45925</v>
       </c>
@@ -3761,7 +3767,7 @@
         <v>6504</v>
       </c>
       <c r="D149" s="13">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E149" s="7">
         <v>463.54</v>
@@ -3771,7 +3777,7 @@
       </c>
       <c r="G149" s="13"/>
     </row>
-    <row r="150" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A150" s="9">
         <v>45926</v>
       </c>
@@ -3782,7 +3788,7 @@
         <v>7192</v>
       </c>
       <c r="D150" s="13">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E150" s="7">
         <v>571.95000000000005</v>
@@ -3792,7 +3798,7 @@
       </c>
       <c r="G150" s="13"/>
     </row>
-    <row r="151" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A151" s="9">
         <v>45927</v>
       </c>
@@ -3803,7 +3809,7 @@
         <v>6392</v>
       </c>
       <c r="D151" s="13">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E151" s="7">
         <v>435.27</v>
@@ -3813,7 +3819,7 @@
       </c>
       <c r="G151" s="13"/>
     </row>
-    <row r="152" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A152" s="9">
         <v>45928</v>
       </c>
@@ -3824,7 +3830,7 @@
         <v>6118</v>
       </c>
       <c r="D152" s="13">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E152" s="7">
         <v>469.64</v>
@@ -3836,7 +3842,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A153" s="9">
         <v>45929</v>
       </c>
@@ -3847,7 +3853,7 @@
         <v>4316</v>
       </c>
       <c r="D153" s="13">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E153" s="7">
         <v>136.32</v>
@@ -3857,7 +3863,7 @@
       </c>
       <c r="G153" s="13"/>
     </row>
-    <row r="154" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>45930</v>
       </c>
@@ -3868,7 +3874,7 @@
         <v>4051</v>
       </c>
       <c r="D154" s="13">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E154" s="7">
         <v>193.01</v>
@@ -3878,7 +3884,7 @@
       </c>
       <c r="G154" s="13"/>
     </row>
-    <row r="155" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A155" s="9">
         <v>45931</v>
       </c>
@@ -3897,7 +3903,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A156" s="9">
         <v>45932</v>
       </c>
@@ -3914,7 +3920,7 @@
       </c>
       <c r="G156" s="15"/>
     </row>
-    <row r="157" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A157" s="9">
         <v>45933</v>
       </c>
@@ -3931,7 +3937,7 @@
       </c>
       <c r="G157" s="15"/>
     </row>
-    <row r="158" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A158" s="9">
         <v>45934</v>
       </c>
@@ -3948,7 +3954,7 @@
       </c>
       <c r="G158" s="15"/>
     </row>
-    <row r="159" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A159" s="9">
         <v>45935</v>
       </c>
@@ -3965,7 +3971,7 @@
       </c>
       <c r="G159" s="15"/>
     </row>
-    <row r="160" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A160" s="9">
         <v>45936</v>
       </c>
@@ -3982,7 +3988,7 @@
       </c>
       <c r="G160" s="16"/>
     </row>
-    <row r="161" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A161" s="9">
         <v>45937</v>
       </c>
@@ -4003,7 +4009,7 @@
       </c>
       <c r="G161" s="13"/>
     </row>
-    <row r="162" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A162" s="9">
         <v>45938</v>
       </c>
@@ -4024,7 +4030,7 @@
       </c>
       <c r="G162" s="13"/>
     </row>
-    <row r="163" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A163" s="9">
         <v>45939</v>
       </c>
@@ -4045,7 +4051,7 @@
       </c>
       <c r="G163" s="13"/>
     </row>
-    <row r="164" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A164" s="9">
         <v>45940</v>
       </c>
@@ -4066,7 +4072,7 @@
       </c>
       <c r="G164" s="13"/>
     </row>
-    <row r="165" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A165" s="9">
         <v>45941</v>
       </c>
@@ -4087,7 +4093,7 @@
       </c>
       <c r="G165" s="13"/>
     </row>
-    <row r="166" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A166" s="9">
         <v>45942</v>
       </c>
@@ -4108,7 +4114,7 @@
       </c>
       <c r="G166" s="13"/>
     </row>
-    <row r="167" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A167" s="9">
         <v>45943</v>
       </c>
@@ -4129,7 +4135,7 @@
       </c>
       <c r="G167" s="13"/>
     </row>
-    <row r="168" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>45944</v>
       </c>
@@ -4150,7 +4156,7 @@
       </c>
       <c r="G168" s="13"/>
     </row>
-    <row r="169" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A169" s="9">
         <v>45945</v>
       </c>
@@ -4171,7 +4177,7 @@
       </c>
       <c r="G169" s="13"/>
     </row>
-    <row r="170" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A170" s="9">
         <v>45946</v>
       </c>
@@ -4192,7 +4198,7 @@
       </c>
       <c r="G170" s="13"/>
     </row>
-    <row r="171" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A171" s="9">
         <v>45947</v>
       </c>
@@ -4211,7 +4217,7 @@
       </c>
       <c r="G171" s="13"/>
     </row>
-    <row r="172" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A172" s="9">
         <v>45948</v>
       </c>
@@ -4230,7 +4236,7 @@
       </c>
       <c r="G172" s="13"/>
     </row>
-    <row r="173" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A173" s="9">
         <v>45949</v>
       </c>
@@ -4251,7 +4257,7 @@
       </c>
       <c r="G173" s="13"/>
     </row>
-    <row r="174" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A174" s="9">
         <v>45950</v>
       </c>
@@ -4270,7 +4276,7 @@
       </c>
       <c r="G174" s="13"/>
     </row>
-    <row r="175" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A175" s="9">
         <v>45951</v>
       </c>
@@ -4291,7 +4297,7 @@
       </c>
       <c r="G175" s="13"/>
     </row>
-    <row r="176" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A176" s="9">
         <v>45952</v>
       </c>
@@ -4312,7 +4318,7 @@
       </c>
       <c r="G176" s="13"/>
     </row>
-    <row r="177" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A177" s="9">
         <v>45953</v>
       </c>
@@ -4331,7 +4337,7 @@
       </c>
       <c r="G177" s="13"/>
     </row>
-    <row r="178" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A178" s="9">
         <v>45954</v>
       </c>
@@ -4352,7 +4358,7 @@
       </c>
       <c r="G178" s="13"/>
     </row>
-    <row r="179" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A179" s="9">
         <v>45955</v>
       </c>
@@ -4371,7 +4377,7 @@
       </c>
       <c r="G179" s="13"/>
     </row>
-    <row r="180" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A180" s="9">
         <v>45956</v>
       </c>
@@ -4392,7 +4398,7 @@
       </c>
       <c r="G180" s="13"/>
     </row>
-    <row r="181" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A181" s="9">
         <v>45957</v>
       </c>
@@ -4413,7 +4419,7 @@
       </c>
       <c r="G181" s="13"/>
     </row>
-    <row r="182" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A182" s="9">
         <v>45958</v>
       </c>
@@ -4434,7 +4440,7 @@
       </c>
       <c r="G182" s="13"/>
     </row>
-    <row r="183" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A183" s="9">
         <v>45959</v>
       </c>
@@ -4455,7 +4461,7 @@
       </c>
       <c r="G183" s="13"/>
     </row>
-    <row r="184" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A184" s="9">
         <v>45960</v>
       </c>
@@ -4476,7 +4482,7 @@
       </c>
       <c r="G184" s="13"/>
     </row>
-    <row r="185" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A185" s="9">
         <v>45961</v>
       </c>
@@ -4497,7 +4503,7 @@
       </c>
       <c r="G185" s="13"/>
     </row>
-    <row r="186" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A186" s="9">
         <v>45962</v>
       </c>
@@ -4516,7 +4522,7 @@
       </c>
       <c r="G186" s="13"/>
     </row>
-    <row r="187" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A187" s="9">
         <v>45963</v>
       </c>
@@ -4535,7 +4541,7 @@
       </c>
       <c r="G187" s="13"/>
     </row>
-    <row r="188" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A188" s="9">
         <v>45964</v>
       </c>
@@ -4556,7 +4562,7 @@
       </c>
       <c r="G188" s="13"/>
     </row>
-    <row r="189" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A189" s="9">
         <v>45965</v>
       </c>
@@ -4577,7 +4583,7 @@
       </c>
       <c r="G189" s="13"/>
     </row>
-    <row r="190" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A190" s="9">
         <v>45966</v>
       </c>
@@ -4598,7 +4604,7 @@
       </c>
       <c r="G190" s="13"/>
     </row>
-    <row r="191" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A191" s="9">
         <v>45967</v>
       </c>
@@ -4619,7 +4625,7 @@
       </c>
       <c r="G191" s="13"/>
     </row>
-    <row r="192" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A192" s="9">
         <v>45968</v>
       </c>
@@ -4640,7 +4646,7 @@
       </c>
       <c r="G192" s="13"/>
     </row>
-    <row r="193" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A193" s="9">
         <v>45969</v>
       </c>
@@ -4661,7 +4667,7 @@
       </c>
       <c r="G193" s="13"/>
     </row>
-    <row r="194" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A194" s="9">
         <v>45970</v>
       </c>
@@ -4682,7 +4688,7 @@
       </c>
       <c r="G194" s="13"/>
     </row>
-    <row r="195" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A195" s="9">
         <v>45971</v>
       </c>
@@ -4703,7 +4709,7 @@
       </c>
       <c r="G195" s="13"/>
     </row>
-    <row r="196" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A196" s="9">
         <v>45972</v>
       </c>
@@ -4724,7 +4730,7 @@
       </c>
       <c r="G196" s="13"/>
     </row>
-    <row r="197" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A197" s="9">
         <v>45973</v>
       </c>
@@ -4745,7 +4751,7 @@
       </c>
       <c r="G197" s="13"/>
     </row>
-    <row r="198" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A198" s="9">
         <v>45974</v>
       </c>
@@ -4766,7 +4772,7 @@
       </c>
       <c r="G198" s="13"/>
     </row>
-    <row r="199" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A199" s="9">
         <v>45975</v>
       </c>
@@ -4787,7 +4793,7 @@
       </c>
       <c r="G199" s="13"/>
     </row>
-    <row r="200" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A200" s="9">
         <v>45976</v>
       </c>
@@ -4808,7 +4814,7 @@
       </c>
       <c r="G200" s="13"/>
     </row>
-    <row r="201" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A201" s="9">
         <v>45977</v>
       </c>
@@ -4823,7 +4829,7 @@
       </c>
       <c r="G201" s="13"/>
     </row>
-    <row r="202" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A202" s="9">
         <v>45978</v>
       </c>
@@ -4838,7 +4844,7 @@
       </c>
       <c r="G202" s="13"/>
     </row>
-    <row r="203" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A203" s="9">
         <v>45979</v>
       </c>
@@ -4853,7 +4859,7 @@
       </c>
       <c r="G203" s="13"/>
     </row>
-    <row r="204" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A204" s="9">
         <v>45980</v>
       </c>
@@ -4868,7 +4874,7 @@
       </c>
       <c r="G204" s="13"/>
     </row>
-    <row r="205" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A205" s="9">
         <v>45981</v>
       </c>
@@ -4883,7 +4889,7 @@
       </c>
       <c r="G205" s="13"/>
     </row>
-    <row r="206" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A206" s="9">
         <v>45982</v>
       </c>
@@ -4898,7 +4904,7 @@
       </c>
       <c r="G206" s="13"/>
     </row>
-    <row r="207" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A207" s="9">
         <v>45983</v>
       </c>
@@ -4913,7 +4919,7 @@
       </c>
       <c r="G207" s="13"/>
     </row>
-    <row r="208" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A208" s="9">
         <v>45984</v>
       </c>
@@ -4928,7 +4934,7 @@
       </c>
       <c r="G208" s="13"/>
     </row>
-    <row r="209" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A209" s="9">
         <v>45985</v>
       </c>
@@ -4943,7 +4949,7 @@
       </c>
       <c r="G209" s="13"/>
     </row>
-    <row r="210" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A210" s="9">
         <v>45986</v>
       </c>
@@ -4958,7 +4964,7 @@
       </c>
       <c r="G210" s="13"/>
     </row>
-    <row r="211" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A211" s="9">
         <v>45987</v>
       </c>
@@ -4973,7 +4979,7 @@
       </c>
       <c r="G211" s="13"/>
     </row>
-    <row r="212" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A212" s="9">
         <v>45988</v>
       </c>
@@ -4988,7 +4994,7 @@
       </c>
       <c r="G212" s="13"/>
     </row>
-    <row r="213" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A213" s="9">
         <v>45989</v>
       </c>
@@ -5003,7 +5009,7 @@
       </c>
       <c r="G213" s="13"/>
     </row>
-    <row r="214" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A214" s="9">
         <v>45990</v>
       </c>
@@ -5018,7 +5024,7 @@
       </c>
       <c r="G214" s="13"/>
     </row>
-    <row r="215" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A215" s="9">
         <v>45991</v>
       </c>
@@ -5033,7 +5039,7 @@
       </c>
       <c r="G215" s="13"/>
     </row>
-    <row r="216" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A216" s="9">
         <v>45992</v>
       </c>
@@ -5048,7 +5054,7 @@
       </c>
       <c r="G216" s="13"/>
     </row>
-    <row r="217" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A217" s="9">
         <v>45993</v>
       </c>
@@ -5063,7 +5069,7 @@
       </c>
       <c r="G217" s="13"/>
     </row>
-    <row r="218" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A218" s="9">
         <v>45994</v>
       </c>
@@ -5078,7 +5084,7 @@
       </c>
       <c r="G218" s="13"/>
     </row>
-    <row r="219" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A219" s="9">
         <v>45995</v>
       </c>
@@ -5093,7 +5099,7 @@
       </c>
       <c r="G219" s="13"/>
     </row>
-    <row r="220" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A220" s="9">
         <v>45996</v>
       </c>
@@ -5108,7 +5114,7 @@
       </c>
       <c r="G220" s="13"/>
     </row>
-    <row r="221" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A221" s="9">
         <v>45997</v>
       </c>
@@ -5123,7 +5129,7 @@
       </c>
       <c r="G221" s="13"/>
     </row>
-    <row r="222" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A222" s="9">
         <v>45998</v>
       </c>
@@ -5138,7 +5144,7 @@
       </c>
       <c r="G222" s="13"/>
     </row>
-    <row r="223" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A223" s="9">
         <v>45999</v>
       </c>
@@ -5153,7 +5159,7 @@
       </c>
       <c r="G223" s="13"/>
     </row>
-    <row r="224" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A224" s="9">
         <v>46000</v>
       </c>
@@ -5168,7 +5174,7 @@
       </c>
       <c r="G224" s="13"/>
     </row>
-    <row r="225" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A225" s="9">
         <v>46001</v>
       </c>
@@ -5183,7 +5189,7 @@
       </c>
       <c r="G225" s="13"/>
     </row>
-    <row r="226" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A226" s="9">
         <v>46002</v>
       </c>
@@ -5198,7 +5204,7 @@
       </c>
       <c r="G226" s="13"/>
     </row>
-    <row r="227" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A227" s="9">
         <v>46003</v>
       </c>
@@ -5213,7 +5219,7 @@
       </c>
       <c r="G227" s="13"/>
     </row>
-    <row r="228" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A228" s="9">
         <v>46004</v>
       </c>
@@ -5228,7 +5234,7 @@
       </c>
       <c r="G228" s="13"/>
     </row>
-    <row r="229" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A229" s="9">
         <v>46005</v>
       </c>
@@ -5243,7 +5249,7 @@
       </c>
       <c r="G229" s="13"/>
     </row>
-    <row r="230" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A230" s="9">
         <v>46006</v>
       </c>
@@ -5258,7 +5264,7 @@
       </c>
       <c r="G230" s="13"/>
     </row>
-    <row r="231" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A231" s="9">
         <v>46007</v>
       </c>
@@ -5273,7 +5279,7 @@
       </c>
       <c r="G231" s="13"/>
     </row>
-    <row r="232" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A232" s="9">
         <v>46008</v>
       </c>
@@ -5288,7 +5294,7 @@
       </c>
       <c r="G232" s="13"/>
     </row>
-    <row r="233" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A233" s="9">
         <v>46009</v>
       </c>
@@ -5303,7 +5309,7 @@
       </c>
       <c r="G233" s="13"/>
     </row>
-    <row r="234" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A234" s="9">
         <v>46010</v>
       </c>
@@ -5318,7 +5324,7 @@
       </c>
       <c r="G234" s="13"/>
     </row>
-    <row r="235" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A235" s="9">
         <v>46011</v>
       </c>
@@ -5333,7 +5339,7 @@
       </c>
       <c r="G235" s="13"/>
     </row>
-    <row r="236" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A236" s="9">
         <v>46012</v>
       </c>
@@ -5354,7 +5360,7 @@
       </c>
       <c r="G236" s="13"/>
     </row>
-    <row r="237" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A237" s="9">
         <v>46013</v>
       </c>
@@ -5375,7 +5381,7 @@
       </c>
       <c r="G237" s="13"/>
     </row>
-    <row r="238" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A238" s="9">
         <v>46014</v>
       </c>
@@ -5396,7 +5402,7 @@
       </c>
       <c r="G238" s="13"/>
     </row>
-    <row r="239" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A239" s="9">
         <v>46015</v>
       </c>
@@ -5417,7 +5423,7 @@
       </c>
       <c r="G239" s="13"/>
     </row>
-    <row r="240" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A240" s="9">
         <v>46016</v>
       </c>
@@ -5438,7 +5444,7 @@
       </c>
       <c r="G240" s="13"/>
     </row>
-    <row r="241" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A241" s="9">
         <v>46017</v>
       </c>
@@ -5459,7 +5465,7 @@
       </c>
       <c r="G241" s="13"/>
     </row>
-    <row r="242" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A242" s="9">
         <v>46018</v>
       </c>
@@ -5480,7 +5486,7 @@
       </c>
       <c r="G242" s="13"/>
     </row>
-    <row r="243" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A243" s="9">
         <v>46019</v>
       </c>
@@ -5501,7 +5507,7 @@
       </c>
       <c r="G243" s="13"/>
     </row>
-    <row r="244" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A244" s="9">
         <v>46020</v>
       </c>
@@ -5522,7 +5528,7 @@
       </c>
       <c r="G244" s="13"/>
     </row>
-    <row r="245" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A245" s="9">
         <v>46021</v>
       </c>
@@ -5543,7 +5549,7 @@
       </c>
       <c r="G245" s="13"/>
     </row>
-    <row r="246" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A246" s="9">
         <v>46022</v>
       </c>
@@ -5564,7 +5570,7 @@
       </c>
       <c r="G246" s="13"/>
     </row>
-    <row r="247" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A247" s="9">
         <v>46023</v>
       </c>
@@ -5585,7 +5591,7 @@
       </c>
       <c r="G247" s="13"/>
     </row>
-    <row r="248" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A248" s="9">
         <v>46024</v>
       </c>
@@ -5606,7 +5612,7 @@
       </c>
       <c r="G248" s="13"/>
     </row>
-    <row r="249" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A249" s="9">
         <v>46025</v>
       </c>
@@ -5627,7 +5633,7 @@
       </c>
       <c r="G249" s="13"/>
     </row>
-    <row r="250" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A250" s="9">
         <v>46026</v>
       </c>
@@ -5648,7 +5654,7 @@
       </c>
       <c r="G250" s="13"/>
     </row>
-    <row r="251" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A251" s="9">
         <v>46027</v>
       </c>
@@ -5669,7 +5675,7 @@
       </c>
       <c r="G251" s="13"/>
     </row>
-    <row r="252" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A252" s="9">
         <v>46028</v>
       </c>
@@ -5690,7 +5696,7 @@
       </c>
       <c r="G252" s="13"/>
     </row>
-    <row r="253" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A253" s="9">
         <v>46029</v>
       </c>
@@ -5711,7 +5717,7 @@
       </c>
       <c r="G253" s="13"/>
     </row>
-    <row r="254" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A254" s="9">
         <v>46030</v>
       </c>
@@ -5732,7 +5738,7 @@
       </c>
       <c r="G254" s="13"/>
     </row>
-    <row r="255" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A255" s="9">
         <v>46031</v>
       </c>
@@ -5753,7 +5759,7 @@
       </c>
       <c r="G255" s="13"/>
     </row>
-    <row r="256" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A256" s="9">
         <v>46032</v>
       </c>
@@ -5774,7 +5780,7 @@
       </c>
       <c r="G256" s="13"/>
     </row>
-    <row r="257" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A257" s="9">
         <v>46033</v>
       </c>
@@ -5795,7 +5801,7 @@
       </c>
       <c r="G257" s="13"/>
     </row>
-    <row r="258" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A258" s="9">
         <v>46034</v>
       </c>
@@ -5816,7 +5822,7 @@
       </c>
       <c r="G258" s="13"/>
     </row>
-    <row r="259" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A259" s="9">
         <v>46035</v>
       </c>
@@ -5837,7 +5843,7 @@
       </c>
       <c r="G259" s="13"/>
     </row>
-    <row r="260" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A260" s="9">
         <v>46036</v>
       </c>
@@ -5858,7 +5864,7 @@
       </c>
       <c r="G260" s="13"/>
     </row>
-    <row r="261" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A261" s="9">
         <v>46037</v>
       </c>
@@ -5879,7 +5885,7 @@
       </c>
       <c r="G261" s="13"/>
     </row>
-    <row r="262" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A262" s="9">
         <v>46038</v>
       </c>
@@ -5900,7 +5906,7 @@
       </c>
       <c r="G262" s="13"/>
     </row>
-    <row r="263" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A263" s="9">
         <v>46039</v>
       </c>
@@ -5921,7 +5927,7 @@
       </c>
       <c r="G263" s="13"/>
     </row>
-    <row r="264" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A264" s="9">
         <v>46040</v>
       </c>
@@ -5942,7 +5948,7 @@
       </c>
       <c r="G264" s="13"/>
     </row>
-    <row r="265" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A265" s="9">
         <v>46041</v>
       </c>
@@ -5963,7 +5969,7 @@
       </c>
       <c r="G265" s="13"/>
     </row>
-    <row r="266" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A266" s="9">
         <v>46042</v>
       </c>
@@ -5984,7 +5990,7 @@
       </c>
       <c r="G266" s="13"/>
     </row>
-    <row r="267" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A267" s="9">
         <v>46043</v>
       </c>
@@ -6005,7 +6011,7 @@
       </c>
       <c r="G267" s="13"/>
     </row>
-    <row r="268" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A268" s="9">
         <v>46044</v>
       </c>
@@ -6026,7 +6032,7 @@
       </c>
       <c r="G268" s="13"/>
     </row>
-    <row r="269" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A269" s="9">
         <v>46045</v>
       </c>
@@ -6047,7 +6053,7 @@
       </c>
       <c r="G269" s="13"/>
     </row>
-    <row r="270" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A270" s="9">
         <v>46046</v>
       </c>
@@ -6068,7 +6074,7 @@
       </c>
       <c r="G270" s="13"/>
     </row>
-    <row r="271" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A271" s="9">
         <v>46047</v>
       </c>
@@ -6089,7 +6095,7 @@
       </c>
       <c r="G271" s="13"/>
     </row>
-    <row r="272" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A272" s="9">
         <v>46048</v>
       </c>
@@ -6110,7 +6116,7 @@
       </c>
       <c r="G272" s="13"/>
     </row>
-    <row r="273" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A273" s="9">
         <v>46049</v>
       </c>
@@ -6131,7 +6137,7 @@
       </c>
       <c r="G273" s="13"/>
     </row>
-    <row r="274" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A274" s="9">
         <v>46050</v>
       </c>
@@ -6152,7 +6158,7 @@
       </c>
       <c r="G274" s="13"/>
     </row>
-    <row r="275" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A275" s="9">
         <v>46051</v>
       </c>
@@ -6173,7 +6179,7 @@
       </c>
       <c r="G275" s="13"/>
     </row>
-    <row r="276" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A276" s="9">
         <v>46052</v>
       </c>
@@ -6194,7 +6200,7 @@
       </c>
       <c r="G276" s="13"/>
     </row>
-    <row r="277" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A277" s="9">
         <v>46053</v>
       </c>
@@ -6215,7 +6221,7 @@
       </c>
       <c r="G277" s="13"/>
     </row>
-    <row r="278" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A278" s="9">
         <v>46054</v>
       </c>
@@ -6236,7 +6242,7 @@
       </c>
       <c r="G278" s="13"/>
     </row>
-    <row r="279" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A279" s="9">
         <v>46055</v>
       </c>
@@ -6257,7 +6263,7 @@
       </c>
       <c r="G279" s="13"/>
     </row>
-    <row r="280" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A280" s="9">
         <v>46056</v>
       </c>
@@ -6278,7 +6284,7 @@
       </c>
       <c r="G280" s="13"/>
     </row>
-    <row r="281" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A281" s="9">
         <v>46057</v>
       </c>
@@ -6299,7 +6305,7 @@
       </c>
       <c r="G281" s="13"/>
     </row>
-    <row r="282" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A282" s="9">
         <v>46058</v>
       </c>
@@ -6320,7 +6326,7 @@
       </c>
       <c r="G282" s="13"/>
     </row>
-    <row r="283" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A283" s="9">
         <v>46059</v>
       </c>
@@ -6341,7 +6347,7 @@
       </c>
       <c r="G283" s="13"/>
     </row>
-    <row r="284" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A284" s="9">
         <v>46060</v>
       </c>
@@ -6362,7 +6368,7 @@
       </c>
       <c r="G284" s="13"/>
     </row>
-    <row r="285" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A285" s="9">
         <v>46061</v>
       </c>
@@ -6383,7 +6389,7 @@
       </c>
       <c r="G285" s="13"/>
     </row>
-    <row r="286" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A286" s="9">
         <v>46062</v>
       </c>
@@ -6404,7 +6410,7 @@
       </c>
       <c r="G286" s="13"/>
     </row>
-    <row r="287" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A287" s="9">
         <v>46063</v>
       </c>
@@ -6425,7 +6431,7 @@
       </c>
       <c r="G287" s="13"/>
     </row>
-    <row r="288" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A288" s="9">
         <v>46064</v>
       </c>
@@ -6446,7 +6452,7 @@
       </c>
       <c r="G288" s="13"/>
     </row>
-    <row r="289" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A289" s="9">
         <v>46065</v>
       </c>
@@ -6467,7 +6473,7 @@
       </c>
       <c r="G289" s="13"/>
     </row>
-    <row r="290" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A290" s="9">
         <v>46066</v>
       </c>
@@ -6484,7 +6490,7 @@
       </c>
       <c r="G290" s="13"/>
     </row>
-    <row r="291" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A291" s="9">
         <v>46067</v>
       </c>
@@ -6501,7 +6507,7 @@
       </c>
       <c r="G291" s="13"/>
     </row>
-    <row r="292" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A292" s="9">
         <v>46068</v>
       </c>
@@ -6518,7 +6524,7 @@
       </c>
       <c r="G292" s="13"/>
     </row>
-    <row r="293" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A293" s="9">
         <v>46069</v>
       </c>
@@ -6535,7 +6541,7 @@
       </c>
       <c r="G293" s="13"/>
     </row>
-    <row r="294" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A294" s="9">
         <v>46070</v>
       </c>
@@ -6552,7 +6558,7 @@
       </c>
       <c r="G294" s="13"/>
     </row>
-    <row r="295" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A295" s="9">
         <v>46071</v>
       </c>
@@ -6569,7 +6575,7 @@
       </c>
       <c r="G295" s="13"/>
     </row>
-    <row r="296" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A296" s="9">
         <v>46072</v>
       </c>
@@ -6586,7 +6592,7 @@
       </c>
       <c r="G296" s="13"/>
     </row>
-    <row r="297" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A297" s="9">
         <v>46073</v>
       </c>
@@ -6603,7 +6609,7 @@
       </c>
       <c r="G297" s="13"/>
     </row>
-    <row r="298" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A298" s="9">
         <v>46074</v>
       </c>
@@ -6620,7 +6626,7 @@
       </c>
       <c r="G298" s="13"/>
     </row>
-    <row r="299" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A299" s="9">
         <v>46075</v>
       </c>
@@ -6637,7 +6643,7 @@
       </c>
       <c r="G299" s="13"/>
     </row>
-    <row r="300" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A300" s="9">
         <v>46076</v>
       </c>
@@ -6654,7 +6660,7 @@
       </c>
       <c r="G300" s="13"/>
     </row>
-    <row r="301" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A301" s="9">
         <v>46077</v>
       </c>
@@ -6671,7 +6677,7 @@
       </c>
       <c r="G301" s="13"/>
     </row>
-    <row r="302" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A302" s="9">
         <v>46078</v>
       </c>
@@ -6688,7 +6694,7 @@
       </c>
       <c r="G302" s="13"/>
     </row>
-    <row r="303" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A303" s="9">
         <v>46079</v>
       </c>
@@ -6705,7 +6711,7 @@
       </c>
       <c r="G303" s="13"/>
     </row>
-    <row r="304" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A304" s="9">
         <v>46080</v>
       </c>
@@ -6722,7 +6728,7 @@
       </c>
       <c r="G304" s="13"/>
     </row>
-    <row r="305" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A305" s="9">
         <v>46081</v>
       </c>
@@ -6739,7 +6745,7 @@
       </c>
       <c r="G305" s="13"/>
     </row>
-    <row r="306" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A306" s="9">
         <v>46082</v>
       </c>
@@ -6756,7 +6762,7 @@
       </c>
       <c r="G306" s="13"/>
     </row>
-    <row r="307" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A307" s="9">
         <v>46083</v>
       </c>
@@ -6777,7 +6783,7 @@
       </c>
       <c r="G307" s="13"/>
     </row>
-    <row r="308" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A308" s="9">
         <v>46084</v>
       </c>
@@ -6798,7 +6804,7 @@
       </c>
       <c r="G308" s="13"/>
     </row>
-    <row r="309" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A309" s="9">
         <v>46085</v>
       </c>
@@ -6819,7 +6825,7 @@
       </c>
       <c r="G309" s="13"/>
     </row>
-    <row r="310" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A310" s="9">
         <v>46086</v>
       </c>
@@ -6840,7 +6846,7 @@
       </c>
       <c r="G310" s="13"/>
     </row>
-    <row r="311" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A311" s="9">
         <v>46087</v>
       </c>
@@ -6861,7 +6867,7 @@
       </c>
       <c r="G311" s="13"/>
     </row>
-    <row r="312" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A312" s="9">
         <v>46088</v>
       </c>
@@ -6882,7 +6888,7 @@
       </c>
       <c r="G312" s="13"/>
     </row>
-    <row r="313" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A313" s="9">
         <v>46089</v>
       </c>
@@ -6903,7 +6909,7 @@
       </c>
       <c r="G313" s="13"/>
     </row>
-    <row r="314" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A314" s="9">
         <v>46090</v>
       </c>
@@ -6924,7 +6930,7 @@
       </c>
       <c r="G314" s="13"/>
     </row>
-    <row r="315" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A315" s="9">
         <v>46091</v>
       </c>
@@ -6945,7 +6951,7 @@
       </c>
       <c r="G315" s="13"/>
     </row>
-    <row r="316" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A316" s="9">
         <v>46092</v>
       </c>
@@ -6969,7 +6975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A317" s="9">
         <v>46093</v>
       </c>
@@ -6990,7 +6996,7 @@
       </c>
       <c r="G317" s="13"/>
     </row>
-    <row r="318" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A318" s="9">
         <v>46094</v>
       </c>
@@ -7017,5 +7023,6 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>